--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_335_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_335_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M2" t="n">
         <v>8</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
         <v>11</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1338,7 +1338,7 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
         <v>5</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
         <v>2</v>
@@ -2122,7 +2122,7 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2321,10 +2321,10 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2517,10 +2517,10 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X23" t="n">
         <v>2</v>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2903,10 +2903,10 @@
         <v>18</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -3099,7 +3099,7 @@
         <v>14</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -3295,7 +3295,7 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>115</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U30" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X30" t="n">
         <v>28</v>
@@ -4295,7 +4295,7 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -4491,7 +4491,7 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -4684,16 +4684,16 @@
         <v>35</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X37" t="n">
         <v>3</v>
@@ -4880,7 +4880,7 @@
         <v>4</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -5275,7 +5275,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -5664,10 +5664,10 @@
         <v>3</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -6056,16 +6056,16 @@
         <v>9</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X44" t="n">
         <v>1</v>
@@ -6784,16 +6784,16 @@
         <v>80</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X48" t="n">
         <v>11</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_335_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_335_EL.xlsx
@@ -674,10 +674,10 @@
         <v>8</v>
       </c>
       <c r="N2" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="P2" t="n">
         <v>7</v>
@@ -833,10 +833,10 @@
         <v>11</v>
       </c>
       <c r="N3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="P3" t="n">
         <v>16</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>84.62</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,14 +1347,14 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA17" t="n">
@@ -1739,14 +1739,14 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -2131,10 +2131,10 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
@@ -2719,10 +2719,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Y25" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -3111,14 +3111,14 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA26" t="n">
@@ -3839,10 +3839,10 @@
         <v>3</v>
       </c>
       <c r="X30" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="Y30" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
@@ -4696,14 +4696,14 @@
         <v>1</v>
       </c>
       <c r="X37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -4892,14 +4892,14 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA38" t="n">
@@ -5872,10 +5872,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
@@ -6796,14 +6796,14 @@
         <v>2</v>
       </c>
       <c r="X48" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Y48" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA48" t="n">
